--- a/provenance/Competency Questions.xlsx
+++ b/provenance/Competency Questions.xlsx
@@ -7,10 +7,12 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competency Questions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Initial Requirements" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Extra" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Initial Requirements" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Competency Questions'!$A$1:$E$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Competency Questions'!$A$1:$F$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Extra'!$A$1:$D$31</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -479,28 +481,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E44"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:F36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
-    <col width="8" customWidth="1" style="4" min="2" max="2"/>
-    <col width="72" customWidth="1" style="4" min="3" max="3"/>
-    <col width="46" bestFit="1" customWidth="1" style="4" min="4" max="4"/>
+    <col width="8" customWidth="1" style="4" min="1" max="1"/>
+    <col width="20" customWidth="1" style="4" min="2" max="2"/>
+    <col width="78" customWidth="1" style="4" min="3" max="3"/>
+    <col width="62" customWidth="1" style="4" min="4" max="4"/>
     <col width="11" customWidth="1" style="4" min="5" max="5"/>
+    <col width="20" customWidth="1" style="4" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Role / Persona</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="B1" s="5" t="inlineStr">
         <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="C1" s="6" t="inlineStr">
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Competency Question</t>
         </is>
@@ -515,53 +518,63 @@
           <t>Operation</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="28.8" customHeight="1" s="4">
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>Ontology</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Assurance engineer</t>
+          <t>CQ-44</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AE-01</t>
-        </is>
-      </c>
-      <c r="C2" s="7" t="inlineStr">
-        <is>
-          <t>What assurance cases are in the store, and what arguments does each contain?</t>
+          <t>Auditor</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>What law or requirement source does the case answer to?</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>read_assurance_case_inventory.rq</t>
+          <t>augmentation/queries/fc01_requirement_source.rq; queries/read_context_in_scope_for_goal.rq</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>read</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>OntoGSN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Assurance engineer</t>
+          <t>CQ-45</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AE-02</t>
-        </is>
-      </c>
-      <c r="C3" s="7" t="inlineStr">
-        <is>
-          <t>How many elements of each GSN type does the case contain?</t>
+          <t>Auditor</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>What system and organisation is this case about?</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>read_case_summary_counts.rq</t>
+          <t>augmentation/queries/fc02_assured_system.rq; queries/read_context_in_scope_for_goal.rq</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -569,80 +582,95 @@
           <t>read</t>
         </is>
       </c>
-    </row>
-    <row r="4" ht="28.8" customHeight="1" s="4">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>OntoGSN</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Assurance engineer</t>
+          <t>CQ-46</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AE-03</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>What is the top goal of each argument - the claim everything else supports?</t>
+          <t>Compliance Officer</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Which low-level claims need development for each system?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>read_top_goals.rq</t>
+          <t>augmentation/queries/fc03_undeveloped_claims_for_system.rq; queries/read_context_in_scope_for_goal.rq; queries/read_undeveloped_elements.rq; queries/read_goals_without_support.rq</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>read</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>OntoGSN</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Assurance engineer</t>
+          <t>CQ-47</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AE-04</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>What does the element with a given identifier say, and what is it linked to?</t>
+          <t>Compliance Officer</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>What controls exist, under which claim, and with what wording?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>read_element_by_identifier.rq</t>
+          <t>queries/read_goal_support_tree.rq</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>read</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>OntoGSN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Assurance engineer</t>
+          <t>CQ-48</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AE-05</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>What is the whole argument beneath a given goal?</t>
+          <t>Compliance Officer</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Which controls still await evidence?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>read_goal_support_tree.rq</t>
+          <t>queries/read_goals_without_support.rq; queries/read_solutions_without_artefact.rq; queries/read_uninstantiated_elements.rq</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -650,26 +678,31 @@
           <t>read</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="28.8" customHeight="1" s="4">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>OntoGSN</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Assurance engineer</t>
+          <t>CQ-49</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AE-06</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>What evidence ultimately supports a given goal?</t>
+          <t>Developer</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Where is the requested evidence kept and how is it fetched?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>read_evidence_supporting_goal.rq</t>
+          <t>augmentation/queries/fc07_evidence_location.rq</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -677,26 +710,31 @@
           <t>read</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="28.8" customHeight="1" s="4">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>OntoGSN-Augmented</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Assurance engineer</t>
+          <t>CQ-50</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AE-07</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>If a given artefact is withdrawn or superseded, which claims are affected?</t>
+          <t>Developer</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Does the evidence exist yet, and how was it produced - by whom, with what, from what?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>read_goals_resting_on_artefact.rq</t>
+          <t>augmentation/queries/fc08_evidence_production.rq</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -704,26 +742,31 @@
           <t>read</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="28.8" customHeight="1" s="4">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>OntoGSN-Augmented</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Assurance engineer</t>
+          <t>CQ-51</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AE-08</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>What context, assumptions and justifications are in scope for a given goal?</t>
+          <t>Process/Software Owner</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Which evidence has been provided?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>read_context_in_scope_for_goal.rq</t>
+          <t>queries/read_evidence_supporting_goal.rq; queries/read_solutions_without_artefact.rq</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -731,26 +774,31 @@
           <t>read</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="28.8" customHeight="1" s="4">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>OntoGSN</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Assurance engineer</t>
+          <t>CQ-52</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AE-09</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>Which lines of argument are declared undeveloped, and are still undeveloped?</t>
+          <t>Process/Software Owner</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Was this evidence verified - by whom, with what mechanism, and did it pass?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>read_undeveloped_elements.rq</t>
+          <t>augmentation/queries/fc10_evidence_verification.rq</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -758,26 +806,31 @@
           <t>read</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="28.8" customHeight="1" s="4">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>OntoGSN-Augmented</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Assurance engineer</t>
+          <t>CQ-53</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AE-10</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>Which goals have no support at all and are not admitted to be undeveloped?</t>
+          <t>Auditor</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Which controls are ready for review?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>read_goals_without_support.rq</t>
+          <t>augmentation/queries/fc11_controls_ready_for_review.rq; queries/read_undeveloped_elements.rq</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -785,26 +838,31 @@
           <t>read</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="28.8" customHeight="1" s="4">
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>OntoGSN</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Assurance engineer</t>
+          <t>CQ-54</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AE-11</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>Which solutions cite no artefact - evidence claimed but not identified?</t>
+          <t>Auditor</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Which controls and evidence have already been positively validated?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>read_solutions_without_artefact.rq</t>
+          <t>queries/read_element_status_flags.rq; queries/read_invalid_elements.rq</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -812,647 +870,767 @@
           <t>read</t>
         </is>
       </c>
-    </row>
-    <row r="13" ht="28.8" customHeight="1" s="4">
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>OntoGSN</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Assurance engineer</t>
+          <t>CQ-55</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AE-12</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>Which artefacts predate a given date, and which claims still rest on them?</t>
+          <t>Auditor</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Is the case fully compliant?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>read_stale_evidence.rq</t>
+          <t>augmentation/queries/fc13_case_compliance.rq</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>read</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>OntoGSN-Augmented</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Assurance engineer</t>
+          <t>CQ-56</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AE-13</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>How is a new, empty assurance case started?</t>
+          <t>Auditor</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Which elements have an open clarification against them?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>create_assurance_case_skeleton.rq</t>
+          <t>augmentation/queries/fc14_open_clarifications.rq</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>create</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="28.8" customHeight="1" s="4">
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>OntoGSN-Augmented</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Assurance engineer</t>
+          <t>CQ-57</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AE-14</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>How is a sub-goal added beneath an existing goal or strategy?</t>
+          <t>Process/Software Owner</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Who can answer for this element - its owner, or the author of its evidence?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>create_goal_under_parent.rq</t>
+          <t>augmentation/queries/fc15_who_answers_for_element.rq</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>create</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="28.8" customHeight="1" s="4">
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>OntoGSN-Augmented</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Assurance engineer</t>
+          <t>CQ-58</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AE-15</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>How is a strategy inserted between a goal and the sub-goals it already has?</t>
+          <t>Auditor</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>What answered a clarification, and which ask did it close?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>create_strategy_between_goals.rq</t>
+          <t>augmentation/queries/fc16_clarification_answers.rq</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>OntoGSN-Augmented</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Assurance engineer</t>
+          <t>CQ-59</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AE-17</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>How is the wording of a claim, strategy or context corrected?</t>
+          <t>Auditor</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>How many rounds has this element taken, and of which kind?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>update_element_statement.rq</t>
+          <t>augmentation/queries/fc17_rounds_per_element.rq</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>OntoGSN-Augmented</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Assurance engineer</t>
+          <t>CQ-60</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AE-23</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>How is an element removed without leaving dangling references to it?</t>
+          <t>Auditor</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Which pending ask was displaced by a newer one?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>delete_element_and_its_links.rq</t>
+          <t>augmentation/queries/fc18_superseded_asks.rq</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>delete</t>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>OntoGSN-Augmented</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Assurance engineer</t>
+          <t>CQ-61</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AE-24</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>How is one support or context link removed, leaving both elements in place?</t>
+          <t>Auditor</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Who currently holds a relayed ask - where is it stuck?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>delete_support_link.rq</t>
+          <t>augmentation/queries/fc19_who_holds_the_ask.rq</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>delete</t>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>OntoGSN-Augmented</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Assurance engineer</t>
+          <t>CQ-62</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AE-25</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>How are the conclusions written by queries/rules/ cleared before re-running them?</t>
+          <t>Auditor</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>How many times was an ask escalated because the holder could not answer?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>delete_materialised_inferences.rq</t>
+          <t>augmentation/queries/fc20_escalation_count.rq</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>delete</t>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>OntoGSN-Augmented</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>CQ-63</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>Auditor</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>AU-01</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>Which elements are not reachable from any top goal - present but unargued?</t>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Which elements are currently in doubt and why?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>read_elements_unreachable_from_top_goal.rq</t>
+          <t>queries/read_challenges_and_their_targets.rq; queries/read_goals_affected_by_challenge.rq</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>read</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>OntoGSN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Auditor</t>
+          <t>CQ-64</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>AU-02</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>What is the current status of every element - valid, true, in doubt, defeated?</t>
+          <t>Compliance Officer</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>What has to be revised, and by whom?</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>read_element_status_flags.rq</t>
+          <t>augmentation/queries/fc22_what_to_revise.rq</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>read</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>OntoGSN-Augmented</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Auditor</t>
+          <t>CQ-65</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AU-03</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>Which elements or relationships are currently invalid, in doubt or defeated?</t>
+          <t>Compliance Officer</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>How many revision rounds, and which revision closed which ask?</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>read_invalid_elements.rq</t>
+          <t>augmentation/queries/fc23_revision_rounds.rq</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>read</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>OntoGSN-Augmented</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Auditor</t>
+          <t>CQ-66</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>AU-04</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>What challenges have been raised, against what, and by what kind of defeater?</t>
+          <t>Developer</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>What did a revision actually change - which artefact replaced which?</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>read_challenges_and_their_targets.rq</t>
+          <t>augmentation/queries/fc24_revision_diff.rq</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>read</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>OntoGSN-Augmented</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>CQ-67</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>Auditor</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>AU-05</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>Which claims above a challenged element lose support if the challenge stands?</t>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Which claims were determined to be insufficient by the report?</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>read_goals_affected_by_challenge.rq</t>
+          <t>queries/read_element_status_flags.rq; queries/read_invalid_elements.rq</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>read</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>OntoGSN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>CQ-68</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>Auditor</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>AU-06</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>Do two distinct elements share a schema:identifier?</t>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>What was left unresolved at the last audit, and what is due by the next one?</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>read_duplicate_identifiers.rq</t>
+          <t>augmentation/queries/fc26_unresolved_at_audit.rq</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>read</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>OntoGSN-Augmented</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>CQ-69</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>Auditor</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>AU-07</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>Does any element support itself through a chain - a circular argument?</t>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Was a resolution implemented, declined, or infeasible?</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>read_support_cycles.rq</t>
+          <t>augmentation/queries/fc27_resolution_state.rq</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>read</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>OntoGSN-Augmented</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Auditor</t>
+          <t>CQ-70</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>AU-08</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>How is a challenge recorded against part of the argument?</t>
+          <t>Developer</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Which evidence needs to be generated manually?</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>create_challenge_to_element.rq</t>
+          <t>augmentation/queries/fc28_manual_evidence.rq</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>OntoGSN-Augmented</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Auditor</t>
+          <t>CQ-71</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>AU-09</t>
-        </is>
-      </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>How is a single element marked invalid?</t>
+          <t>Developer</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Which evidence is generated automatically, and how or where from can it be retrieved?</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>update_mark_element_invalid.rq</t>
+          <t>augmentation/queries/fc29_automated_evidence.rq</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>OntoGSN-Augmented</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Auditor</t>
+          <t>CQ-72</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>AU-14</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>How is a challenge withdrawn, together with the doubt and defeat it caused?</t>
+          <t>Process/Software Owner</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Which evidence needs an alternative provision mechanism - an interview, a call, paper?</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>delete_challenge_and_its_effects.rq</t>
+          <t>augmentation/queries/fc30_alternative_provision.rq</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>delete</t>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>OntoGSN-Augmented</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Auditor</t>
+          <t>CQ-73</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>AU-15</t>
-        </is>
-      </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>How is a whole assurance case and everything under it removed?</t>
+          <t>Developer</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Which evidence cannot be produced at all, as opposed to not yet produced?</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>delete_assurance_case.rq</t>
+          <t>augmentation/queries/fc31_evidence_cannot_be_produced.rq</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>delete</t>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>OntoGSN-Augmented</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Domain expert</t>
+          <t>CQ-74</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DE-01</t>
-        </is>
-      </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>Where are the assurance claim points, and what confidence argument backs each?</t>
+          <t>Auditor</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Which issue cannot be resolved at all, as opposed to not yet resolved?</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>read_assurance_claim_points.rq</t>
+          <t>augmentation/queries/fc32_cannot_resolve.rq</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>read</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>OntoGSN-Augmented</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Domain expert</t>
+          <t>CQ-75</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DE-02</t>
-        </is>
-      </c>
-      <c r="C33" s="7" t="inlineStr">
-        <is>
-          <t>Which assurance claim points have no confidence argument behind them?</t>
+          <t>Compliance Officer</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>How is the interpretation instantiated into claims and evidence?</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>read_claim_points_without_confidence_argument.rq</t>
+          <t>augmentation/queries/fc33_instantiated_elements.rq; queries/read_pattern_instantiations.rq</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>read</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>OntoGSN</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Domain expert</t>
+          <t>CQ-76</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>DE-03</t>
-        </is>
-      </c>
-      <c r="C34" s="7" t="inlineStr">
-        <is>
-          <t>Which modules depend on which, and through which elements?</t>
+          <t>Compliance Officer</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Who is responsible for retrieving the evidence for a particular system?</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>read_module_dependencies.rq</t>
+          <t>augmentation/queries/fc34_who_retrieves_evidence.rq</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>read</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>OntoGSN-Augmented</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Domain expert</t>
+          <t>CQ-77</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>DE-04</t>
-        </is>
-      </c>
-      <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t>Which away elements are referenced, and does the module they come from exist?</t>
+          <t>Developer</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Which artefacts need changing, and who owns the change?</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>read_away_elements.rq</t>
+          <t>augmentation/queries/fc35_artefacts_to_change.rq; queries/read_goals_resting_on_artefact.rq</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>read</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>OntoGSN-Augmented</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Domain expert</t>
+          <t>CQ-78</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DE-05</t>
-        </is>
-      </c>
-      <c r="C36" s="7" t="inlineStr">
-        <is>
-          <t>Which public elements sit inside a contract module, where they must not?</t>
+          <t>Developer</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Which evidence can be generated automatically, and which has been assessed as manual?</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>read_public_elements_in_contract_modules.rq</t>
+          <t>augmentation/queries/fc36_automation_feasibility.rq</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1460,230 +1638,722 @@
           <t>read</t>
         </is>
       </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Domain expert</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>DE-06</t>
-        </is>
-      </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>Which elements instantiate which argument pattern, and is the pattern's own documentation complete?</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>read_pattern_instantiations.rq</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>read</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Domain expert</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>DE-07</t>
-        </is>
-      </c>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t>Which elements are still uninstantiated placeholders from a pattern?</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>read_uninstantiated_elements.rq</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>read</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Domain expert</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>DE-08</t>
-        </is>
-      </c>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t>Which relationships carry pattern decorators - optional, multiple, cardinality?</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>read_relationship_decorators.rq</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>read</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Domain expert</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>DE-09</t>
-        </is>
-      </c>
-      <c r="C40" s="7" t="inlineStr">
-        <is>
-          <t>How is a context element added to a goal or strategy, pointing at an artefact?</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>create_context_for_goal.rq</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>create</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Domain expert</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>DE-10</t>
-        </is>
-      </c>
-      <c r="C41" s="7" t="inlineStr">
-        <is>
-          <t>How is a new piece of evidence attached to a goal?</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>create_solution_with_artefact.rq</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>create</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Domain expert</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>DE-11</t>
-        </is>
-      </c>
-      <c r="C42" s="7" t="inlineStr">
-        <is>
-          <t>How are artefacts already in the store turned into solutions in bulk?</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>create_solutions_for_unreferenced_artefacts.rq</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>create</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Domain expert</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>DE-15</t>
-        </is>
-      </c>
-      <c r="C43" s="7" t="inlineStr">
-        <is>
-          <t>How is a solution repointed when its evidence is superseded by a new version?</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>update_retarget_solution_to_new_artefact.rq</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>update</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Domain expert</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>DE-16</t>
-        </is>
-      </c>
-      <c r="C44" s="7" t="inlineStr">
-        <is>
-          <t>How are artefacts no solution or context cites any more cleared out?</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>delete_unreferenced_artefacts.rq</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>delete</t>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>OntoGSN-Augmented</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E44"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <autoFilter ref="A1:F36"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" style="4" min="1" max="1"/>
+    <col width="78" customWidth="1" style="4" min="2" max="2"/>
+    <col width="62" customWidth="1" style="4" min="3" max="3"/>
+    <col width="11" customWidth="1" style="4" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Competency Question</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>SPARQL Query File</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>Operation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CQ-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>What assurance cases are in the store, and what arguments does each contain?</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>queries/read_assurance_case_inventory.rq</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CQ-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Where are the assurance claim points, and what confidence argument backs each?</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>queries/read_assurance_claim_points.rq</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CQ-03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Which away elements are referenced, and does the module they come from exist?</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>queries/read_away_elements.rq</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CQ-04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>How many elements of each GSN type does the case contain?</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>queries/read_case_summary_counts.rq</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CQ-06</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Which assurance claim points have no confidence argument behind them?</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>queries/read_claim_points_without_confidence_argument.rq</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CQ-08</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Do two distinct elements share a schema:identifier?</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>queries/read_duplicate_identifiers.rq</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CQ-09</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>What does the element with a given identifier say, and what is it linked to?</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>queries/read_element_by_identifier.rq</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CQ-11</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Which elements are not reachable from any top goal - present but unargued?</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>queries/read_elements_unreachable_from_top_goal.rq</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CQ-18</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Which modules depend on which, and through which elements?</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>queries/read_module_dependencies.rq</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CQ-20</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Which public elements sit inside a contract module, where they must not?</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>queries/read_public_elements_in_contract_modules.rq</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CQ-21</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Which relationships carry pattern decorators - optional, multiple, cardinality?</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>queries/read_relationship_decorators.rq</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CQ-23</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Which artefacts predate a given date, and which claims still rest on them?</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>queries/read_stale_evidence.rq</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CQ-24</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Does any element support itself through a chain - a circular argument?</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>queries/read_support_cycles.rq</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CQ-25</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>What is the top goal of each argument - the claim everything else supports?</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>queries/read_top_goals.rq</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CQ-28</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>How is a new, empty assurance case started?</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>queries/create_assurance_case_skeleton.rq</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CQ-29</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>How is a challenge recorded against part of the argument?</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>queries/create_challenge_to_element.rq</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CQ-30</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>How is a context element added to a goal or strategy, pointing at an artefact?</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>queries/create_context_for_goal.rq</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CQ-31</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>How is a sub-goal added beneath an existing goal or strategy?</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>queries/create_goal_under_parent.rq</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CQ-32</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>How is a new piece of evidence attached to a goal?</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>queries/create_solution_with_artefact.rq</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CQ-33</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>How are artefacts already in the store turned into solutions in bulk?</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>queries/create_solutions_for_unreferenced_artefacts.rq</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CQ-34</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>How is a strategy inserted between a goal and the sub-goals it already has?</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>queries/create_strategy_between_goals.rq</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CQ-35</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>How is the wording of a claim, strategy or context corrected?</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>queries/update_element_statement.rq</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CQ-36</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>How is a single element marked invalid?</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>queries/update_mark_element_invalid.rq</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>CQ-37</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>How is a solution repointed when its evidence is superseded by a new version?</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>queries/update_retarget_solution_to_new_artefact.rq</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>CQ-38</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>How is a whole assurance case and everything under it removed?</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>queries/delete_assurance_case.rq</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>delete</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CQ-39</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>How is a challenge withdrawn, together with the doubt and defeat it caused?</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>queries/delete_challenge_and_its_effects.rq</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>delete</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>CQ-40</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>How is an element removed without leaving dangling references to it?</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>queries/delete_element_and_its_links.rq</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>delete</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>CQ-41</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>How are the conclusions written by queries/rules/ cleared before re-running them?</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>queries/delete_materialised_inferences.rq</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>delete</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>CQ-42</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>How is one support or context link removed, leaving both elements in place?</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>queries/delete_support_link.rq</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>delete</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>CQ-43</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>How are artefacts no solution or context cites any more cleared out?</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>queries/delete_unreferenced_artefacts.rq</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>delete</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D31"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
